--- a/data-manipulation-scripts/sheets-cleanup/sheets/ESTICADOR CORRENTE 06_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/ESTICADOR CORRENTE 06_02.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -95,9 +95,6 @@
   </si>
   <si>
     <t>ESTICADOR CORRENTE PECA+ TWISTER/ TORNADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPA ESTICADOR CORRENTE IRON BROS NXR125 150 160 196603 </t>
   </si>
 </sst>
 </file>
@@ -583,12 +580,8 @@
     </row>
     <row r="20">
       <c r="A20" s="4"/>
-      <c r="B20" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
     <row r="21">
@@ -6465,20 +6458,14 @@
       <c r="C999" s="3"/>
       <c r="D999" s="3"/>
     </row>
-    <row r="1000">
-      <c r="A1000" s="4"/>
-      <c r="B1000" s="3"/>
-      <c r="C1000" s="3"/>
-      <c r="D1000" s="3"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A1000">
+  <conditionalFormatting sqref="A1:A999">
     <cfRule type="notContainsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(A1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A1000">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A999">
       <formula1>COUNTIF($A:$A,A1)=1</formula1>
     </dataValidation>
   </dataValidations>
